--- a/tests/fixtures/11_loan_schedule/pattern-from-draft.xlsx
+++ b/tests/fixtures/11_loan_schedule/pattern-from-draft.xlsx
@@ -26,12 +26,42 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0FFD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0E0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D0FF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +76,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,796 +451,984 @@
   </sheetPr>
   <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>currency.sign</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>amt_lbl</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Loan Amount:</t>
         </is>
       </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>rate_lbl</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Monthly Rate:</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>term_lbl</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Term \(months\):</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>start_lbl</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Start Date:</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>col_no</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Payment #</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>col_date</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>col_payment</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Payment</t>
         </is>
       </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>col_principal</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>col_interest</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>col_balance</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>loan.amount</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>loan.rate</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>[0-9.]+%</t>
         </is>
       </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>loan.term</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>[0-9]+</t>
         </is>
       </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>loan.start</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>amort.payment_no</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>[0-9]+</t>
         </is>
       </c>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>amort.date</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>amort.payment</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>amort.principal</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>amort.interest</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>amort.balance</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>summary.label</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>summary.payment</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>summary.principal</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>summary.interest</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>amt_lbl</t>
         </is>
       </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>loan.amount</t>
         </is>
       </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>rate_lbl</t>
         </is>
       </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>loan.rate</t>
         </is>
       </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>term_lbl</t>
         </is>
       </c>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>loan.term</t>
         </is>
       </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>start_lbl</t>
         </is>
       </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>cell:1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>loan.start</t>
         </is>
       </c>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>table:1</t>
         </is>
       </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>col_no</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>col_date</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>col_payment</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>col_principal</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>col_interest</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>col_balance</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
+      <c r="A38" s="3" t="n"/>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>amort.payment_no</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>amort.date</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>amort.payment</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>amort.principal</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>amort.interest</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>amort.balance</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>FOOTER:1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>summary.label</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>summary.payment</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>summary.principal</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>summary.interest</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/fixtures/11_loan_schedule/pattern-from-draft.xlsx
+++ b/tests/fixtures/11_loan_schedule/pattern-from-draft.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Term \(months\):</t>
+          <t>Term (months):</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
